--- a/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-consent.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-55-56---create-examples-for-each-at-aps-profile/StructureDefinition-at-aps-consent.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T12:31:41+00:00</t>
+    <t>2026-01-28T09:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -644,7 +644,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -673,7 +673,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization)
 </t>
   </si>
   <si>
@@ -690,7 +690,7 @@
   </si>
   <si>
     <t>Attachment
-Reference(Consent|4.0.1|DocumentReference|4.0.1|Contract|4.0.1|QuestionnaireResponse|4.0.1)</t>
+Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-consent|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-documentreference|Contract|QuestionnaireResponse)</t>
   </si>
   <si>
     <t>Source from which this consent is taken</t>
@@ -840,7 +840,7 @@
     <t>Consent.verification.verifiedWith</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -944,7 +944,7 @@
     <t>Consent.provision.actor.reference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Group|4.0.1|CareTeam|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|RelatedPerson|4.0.1|PractitionerRole|4.0.1)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-device|Group|CareTeam|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-organization|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-patient|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitioner|RelatedPerson|https://fhir.hl7.at/elga/aps/r4/StructureDefinition/at-aps-practitionerrole)
 </t>
   </si>
   <si>
@@ -1444,7 +1444,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="117.01953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
